--- a/results/Int All Data 0.3/Rando_fi_explain.xlsx
+++ b/results/Int All Data 0.3/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008980314625966079</v>
+        <v>0.001019701775125777</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001902091199679812</v>
+        <v>-0.0003641068047735974</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004028964958837744</v>
+        <v>0.0002691498616299071</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001504382546797389</v>
+        <v>-0.0002878796719800547</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0002483727282614012</v>
+        <v>9.952737828240483e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.001055130229815713</v>
+        <v>0.0005067874889516112</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0001417556301157652</v>
+        <v>-1.010452741163514e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.001931855635351943</v>
+        <v>-0.0009809870355810923</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0007714884800043286</v>
+        <v>-0.0008416721967386045</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004730509963665385</v>
+        <v>-0.0005301250996340733</v>
       </c>
       <c r="L3" t="n">
-        <v>-9.017584006524305e-05</v>
+        <v>-0.0003729192042126839</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.455522248917876e-05</v>
+        <v>0.0005388800957170014</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.003764900747670349</v>
+        <v>0.0001233616650580616</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0006828117656215706</v>
+        <v>-2.938906872048232e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.000391270736415491</v>
+        <v>-0.0002327464406157342</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.002586987490887973</v>
+        <v>0.003580105746730364</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006976366230914877</v>
+        <v>0.0001272281761979544</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001728097036025052</v>
+        <v>-0.00131208995719563</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0005687128945156628</v>
+        <v>-6.834523951889107e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0006289461027049737</v>
+        <v>-0.0002615836422298168</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0001478312952893433</v>
+        <v>-0.0001694981287459874</v>
       </c>
       <c r="W3" t="n">
-        <v>0.000158481010897502</v>
+        <v>0.0007446204495759133</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001378899089430017</v>
+        <v>0.001985469601835903</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.475958875219676e-05</v>
+        <v>-0.0003354274317477124</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001151699323228172</v>
+        <v>0.0003761177343537084</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.001221939373014797</v>
+        <v>-0.0004822237857263711</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.0005126112744897071</v>
+        <v>0.0005591081172192513</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0007921268589168862</v>
+        <v>-0.0008735762460751929</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.00244733823354327</v>
+        <v>0.006329968272477206</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.002295910838079893</v>
+        <v>0.006460160859491026</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001120285061261773</v>
+        <v>-3.227878975183949e-05</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0003072636993271105</v>
+        <v>0.0001029984506962356</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0001351091683244465</v>
+        <v>0.000422037369675493</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0007546374629094754</v>
+        <v>7.926782186980829e-05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.593471662549653e-05</v>
+        <v>0.00145280038931122</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.00522469940299467</v>
+        <v>0.008664135385279029</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4.007798370449289e-05</v>
+        <v>-7.563220711658377e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.002083280978890613</v>
+        <v>0.005161473040179968</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0001206851941933485</v>
+        <v>0.000480124560664733</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.001574378712582483</v>
+        <v>0.0006781272211848895</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0001478038188881814</v>
+        <v>0.0004205930098843692</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-9.606859394044827e-05</v>
+        <v>-0.000329399483018893</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0006049908101351332</v>
+        <v>-0.0002753677404206665</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0003063955032829136</v>
+        <v>0.0002041967168241088</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.002963758915311706</v>
+        <v>0.0001235053293447009</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.0004403659639403611</v>
+        <v>9.225686473007145e-05</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0003606022348269391</v>
+        <v>0.0001972699811454703</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0005606034193019994</v>
+        <v>0.0003269106730727224</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.638092214825364e-05</v>
+        <v>-0.0003183086773990862</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.001556083425831739</v>
+        <v>0.000337037253246314</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.00151032186554061</v>
+        <v>0.002205668336044243</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.004848339081607275</v>
+        <v>0.00641567755787798</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.004148074462434699</v>
+        <v>0.004287589331413812</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.631558239482879e-07</v>
+        <v>0.0003355061332262532</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0001505805229472446</v>
+        <v>0.0002830544433994798</v>
       </c>
       <c r="BE3" t="n">
-        <v>-1.020900554270841e-05</v>
+        <v>0.001517061923982904</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.004691468400408759</v>
+        <v>0.007633605144938242</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.003462338367310752</v>
+        <v>0.001378308205349878</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.0002394673750493548</v>
+        <v>0.000164169443919554</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003799151320940752</v>
+        <v>0.005406182699024891</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0003605098316788647</v>
+        <v>-0.0001660340498035573</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.0004197363540218757</v>
+        <v>-0.001476343397482477</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0005391295601014134</v>
+        <v>-0.000285594880656801</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0003739764923372613</v>
+        <v>-0.0008121991647889737</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.002777485889993808</v>
+        <v>0.006867070005741903</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0001404437442043305</v>
+        <v>-0.0007580866747002313</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0002293282882123582</v>
+        <v>-0.0006958536387439973</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0006960345037339676</v>
+        <v>0.0003055550810649743</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.001328467074372941</v>
+        <v>-0.001631954648632782</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.500406961143625e-05</v>
+        <v>0.000518167802625955</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.0006310785740327007</v>
+        <v>-0.0003300317316044022</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0003080719275187793</v>
+        <v>-0.0009619732767002832</v>
       </c>
       <c r="BW3" t="n">
-        <v>-1.739595174549469e-05</v>
+        <v>3.361895336557841e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.000317729355942279</v>
+        <v>-0.001424314619174894</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.001014568809475507</v>
+        <v>0.0005376692013977924</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0006976654615613209</v>
+        <v>0.000758276389193907</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.0002038417586768448</v>
+        <v>0.0005143688928975221</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0003703731578749092</v>
+        <v>-7.42075204996984e-05</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.610184647710907e-05</v>
+        <v>-0.000255603622669156</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0003839992132573666</v>
+        <v>0.0007337512818320867</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.001307926750442821</v>
+        <v>-0.001360503145147516</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0002801464381668107</v>
+        <v>-0.0005751518151014135</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.000803241154019596</v>
+        <v>-0.001385125969653133</v>
       </c>
       <c r="CH3" t="n">
-        <v>7.707916953181181e-05</v>
+        <v>4.456907549040825e-05</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0008563455076454139</v>
+        <v>-0.001441601822114203</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-1.256254071277385e-05</v>
+        <v>-1.648530394734227e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.001122168562385862</v>
+        <v>4.812831144048726e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.001122014071862952</v>
+        <v>-0.0001979221983082669</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0008005150862290011</v>
+        <v>0.0001823517898792959</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.0003093377167278832</v>
+        <v>0.0002417323182394215</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0004315466589591687</v>
+        <v>-5.024713251094992e-06</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.0001703928532077836</v>
+        <v>0.000145685010873493</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.0007907097644915283</v>
+        <v>0.0001946871519265281</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.0005278065154840072</v>
+        <v>-0.0008063582501053468</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.000552521196311957</v>
+        <v>0.001046328936342634</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.0001461471478087162</v>
+        <v>-0.0005120632431221373</v>
       </c>
       <c r="CU3" t="n">
-        <v>7.179588627624356e-05</v>
+        <v>-9.076515768139171e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0001212012103099858</v>
+        <v>-0.0001390184493331814</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0007702484804214471</v>
+        <v>-0.0003231518236192398</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.0007910763396573506</v>
+        <v>-0.0003103916699720943</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-7.808707290999472e-05</v>
+        <v>-0.0001848146893490121</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0001965593668560028</v>
+        <v>-1.703949691826411e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>8.248012750310619e-05</v>
+        <v>0.0002130895191544224</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.0003765844773943116</v>
+        <v>0.0009489085706036015</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.0002307507468478931</v>
+        <v>-8.21643547568096e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.000601357937180127</v>
+        <v>-0.0003196993622166977</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.001619517992060455</v>
+        <v>-0.001291891524749351</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.0003258852577720861</v>
+        <v>-0.0009104829950886941</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.000548438873665702</v>
+        <v>-0.001358273415195529</v>
       </c>
       <c r="DI3" t="n">
-        <v>-4.6660898820039e-05</v>
+        <v>-0.001629976236614428</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0005645747985211213</v>
+        <v>-0.0005246996042495134</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0006509679217627484</v>
+        <v>-0.0001332646569182893</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0001382346645615373</v>
+        <v>0.0001139073476571828</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.000162672688105473</v>
+        <v>-0.000316501281563003</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.001576446997311036</v>
+        <v>-0.001499417810570877</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.001224665816053058</v>
+        <v>-0.002555176697816351</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.000992504054288398</v>
+        <v>-0.000821517236031606</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.0001393266902251577</v>
+        <v>-1.580768105409968e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0002045899899027359</v>
+        <v>6.435847007299155e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.0001489571303625159</v>
+        <v>-7.312486296477958e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.0008593608603164107</v>
+        <v>-0.0009882618707570845</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.0001026032359196105</v>
+        <v>-0.0008645079514394969</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.0003089094648823265</v>
+        <v>-6.850218767270544e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0006162634203104012</v>
+        <v>-0.0005623695947484952</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.001220983881997928</v>
+        <v>0.000966942891857324</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.749531969601371e-05</v>
+        <v>-4.132447311747554e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0003519664698445635</v>
+        <v>9.57576334291899e-05</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.002729858790650207</v>
+        <v>-0.001997133384171703</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.0001183341412743588</v>
+        <v>4.768472444798719e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0.0003057475442724778</v>
+        <v>-0.000339754475699946</v>
       </c>
       <c r="EE3" t="n">
-        <v>2.938884917104589e-05</v>
+        <v>-4.527203882555564e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.001101104996717272</v>
+        <v>0.0001366150734481519</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0003672266950064296</v>
+        <v>-0.001469699025601515</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.0001517885130043251</v>
+        <v>-6.847795694053796e-06</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.001247654869796488</v>
+        <v>-0.0003063759318542669</v>
       </c>
       <c r="EJ3" t="n">
-        <v>1.111176430983445e-06</v>
+        <v>-8.52120657988509e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0003945765197780437</v>
+        <v>-0.0006262504922402601</v>
       </c>
       <c r="EL3" t="n">
-        <v>-6.706222070406165e-05</v>
+        <v>2.922832981866574e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>-9.161025308043858e-05</v>
+        <v>-3.166303313198449e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0001230060291389101</v>
+        <v>0.0001333165782073564</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-9.271323657903284e-05</v>
+        <v>-3.83580832601682e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0007583998545100589</v>
+        <v>-0.0007162050387740615</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0.0002769618128409579</v>
+        <v>-7.112758767104487e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.0002670143605634679</v>
+        <v>0.0001337845701613905</v>
       </c>
       <c r="ET3" t="n">
-        <v>-6.874526610275873e-05</v>
+        <v>-0.000151447619708528</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.0007494860169221517</v>
+        <v>-0.0003162607225910352</v>
       </c>
       <c r="EV3" t="n">
-        <v>1.745743991535375e-05</v>
+        <v>5.040252342640715e-06</v>
       </c>
       <c r="EW3" t="n">
-        <v>8.447199807188891e-05</v>
+        <v>-0.001110268115261475</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0004642704079013892</v>
+        <v>-0.0002298882629580823</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0001872352095408669</v>
+        <v>-3.547624372654213e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004543915361090264</v>
+        <v>0.0033802271637492</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009023648612562682</v>
+        <v>0.00116921805163338</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001074437464302183</v>
+        <v>0.001199865632402944</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001052172051396323</v>
+        <v>0.001313228346559812</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0005008515062022578</v>
+        <v>0.0003982686690485423</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002440966844340554</v>
+        <v>0.002398186582386571</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001420429512747268</v>
+        <v>0.001310185438778768</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003699764946379343</v>
+        <v>0.003637322401817558</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001127585648243639</v>
+        <v>0.001355827702430208</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001071725393069531</v>
+        <v>0.001204654932686785</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0014642956769066</v>
+        <v>0.001590390411877715</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001884044174907553</v>
+        <v>0.00248374920525215</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006887926082233807</v>
+        <v>0.004735913972641826</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002877548686042613</v>
+        <v>0.002754919245987447</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001270176459916469</v>
+        <v>0.0008840047204915787</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00708789372170375</v>
+        <v>0.004949425903374847</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001347663951793</v>
+        <v>0.001225351335044601</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006301155069050862</v>
+        <v>0.006277453766105241</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001461386689559953</v>
+        <v>0.0009795445811750397</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001467793603306809</v>
+        <v>0.002667772241784397</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00382001428135463</v>
+        <v>0.004389684774395547</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00284472457904435</v>
+        <v>0.002682172700594463</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004919673613014107</v>
+        <v>0.004258343632805975</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0004867858124087462</v>
+        <v>0.0005412466288048429</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.005200836837416441</v>
+        <v>0.003731090125477843</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00492732995862864</v>
+        <v>0.003735010739828478</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001352507980087598</v>
+        <v>0.001032320144043415</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.003581118801250869</v>
+        <v>0.000477546750867886</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.008399891697219483</v>
+        <v>0.009368303727884504</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.01292005938174837</v>
+        <v>0.01350103945947061</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003944504429078337</v>
+        <v>0.002855641906090122</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001162302934569683</v>
+        <v>0.0009247921489391654</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.00116552856697592</v>
+        <v>0.003087216332238943</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.002398359202834753</v>
+        <v>0.002454122427553262</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.008056254329524271</v>
+        <v>0.006876937734912666</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.009042324393460026</v>
+        <v>0.01173569140466569</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.002583192695926027</v>
+        <v>0.001240520047422599</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.005860246316141043</v>
+        <v>0.003872746265579769</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002017832693654067</v>
+        <v>0.003162885953688268</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.00534088058645892</v>
+        <v>0.007645788324309025</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.002026657834034273</v>
+        <v>0.001476049571767493</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.00289134861819629</v>
+        <v>0.002456362835546438</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.01000169503381197</v>
+        <v>0.01204649700490516</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001176829065598326</v>
+        <v>0.001489827581953233</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.004064699740533757</v>
+        <v>0.001445333055051785</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002110455646249107</v>
+        <v>0.002073174155769002</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001377798793064241</v>
+        <v>0.001991674832209546</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002233606523530768</v>
+        <v>0.001647994277668916</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001266523835667266</v>
+        <v>0.0006364857449712017</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001512901505642744</v>
+        <v>0.002517195923161635</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.004446980486454052</v>
+        <v>0.003683319012943623</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01486871961316272</v>
+        <v>0.01370542437010897</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.007669141223203817</v>
+        <v>0.006104402514870684</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0003670758729280754</v>
+        <v>0.0005780301556937969</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0005650387170435088</v>
+        <v>0.0006704248182550908</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.003618209654984356</v>
+        <v>0.004223063359751499</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.009372998587632101</v>
+        <v>0.01109629220139169</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.01001973146273875</v>
+        <v>0.005414966596724962</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001703327610410646</v>
+        <v>0.001377412167377875</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.00685567934589171</v>
+        <v>0.008218651422022414</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001646645700498333</v>
+        <v>0.002909773458864079</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002979857001700261</v>
+        <v>0.003448853389549019</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0009021524464574153</v>
+        <v>0.0009280462451625655</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001214124984701576</v>
+        <v>0.001821236560620745</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.01403551705447912</v>
+        <v>0.01408439313351472</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002667876328033109</v>
+        <v>0.002894458104826141</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.00264032184905819</v>
+        <v>0.001301766797360059</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.00246922067523584</v>
+        <v>0.001324580657053266</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.002384674543182704</v>
+        <v>0.003525501227655427</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0008880547511554795</v>
+        <v>0.001374298582288407</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.00138220267410538</v>
+        <v>0.001579134679833372</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.00102932361527784</v>
+        <v>0.002759472189484186</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001142113954365785</v>
+        <v>5.533711056866978e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001609858439352404</v>
+        <v>0.003413156868705475</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.004675385224666138</v>
+        <v>0.003919958498915657</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004378374542106305</v>
+        <v>0.004629338604242638</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.003092786462328917</v>
+        <v>0.000991222573859891</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001593918024474092</v>
+        <v>0.0008862513218013481</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001437807250733934</v>
+        <v>0.0007063349633436158</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.003877494925206586</v>
+        <v>0.003867629897301919</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.002251297519048349</v>
+        <v>0.003499810539007473</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001945736702968407</v>
+        <v>0.00292112456111189</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.001393304885910824</v>
+        <v>0.00292797066090014</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001440357538356383</v>
+        <v>0.0009200405842120534</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001786676369902622</v>
+        <v>0.002686573390399691</v>
       </c>
       <c r="CJ4" t="n">
-        <v>7.148461793678626e-05</v>
+        <v>0.0001364004299025642</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.003163451381877228</v>
+        <v>0.002767397386523682</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.003196563582577183</v>
+        <v>0.001230868803888994</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001107783030630456</v>
+        <v>0.001633788072143422</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001898998966324476</v>
+        <v>0.001966391269190906</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001188946979513643</v>
+        <v>0.002081070034328007</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0002922514008512988</v>
+        <v>0.0003382495498168844</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002955018749311119</v>
+        <v>0.002596660285955716</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.001490645810635781</v>
+        <v>0.001929131688518989</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.001394282271156629</v>
+        <v>0.003178444877455376</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0009246905458175956</v>
+        <v>0.0006585189280497718</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.00028567448937558</v>
+        <v>0.0006459551485834917</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0003279946394203344</v>
+        <v>0.0005277523712119384</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.002204795055755189</v>
+        <v>0.0007944857785246245</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.001676998077599345</v>
+        <v>0.001921656678742001</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0001781129712755153</v>
+        <v>0.0004750438689611221</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0005397935164221587</v>
+        <v>0.0001889523420199823</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0007469361176770311</v>
+        <v>0.0006985593118309648</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.003459819460390357</v>
+        <v>0.002099167228886991</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0004503842925616411</v>
+        <v>0.0002762419675920971</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001642083525631463</v>
+        <v>0.001776933495994282</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.004797780778746551</v>
+        <v>0.004330803613124873</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.00116904659200748</v>
+        <v>0.001276894465083569</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.003954224416091598</v>
+        <v>0.002654073942787664</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001180378129711535</v>
+        <v>0.003907013686858892</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.003834068216221272</v>
+        <v>0.0009937893165891331</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001029548077264762</v>
+        <v>0.002392278720248971</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0004065596568914877</v>
+        <v>0.0001777531910242573</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.00344545381073419</v>
+        <v>0.001263748661085026</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.003554105992662464</v>
+        <v>0.001902323652143881</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.003732331836784113</v>
+        <v>0.004212140778904481</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.002433923512568146</v>
+        <v>0.002329779721215297</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0004509552323450271</v>
+        <v>0.0002812585365966469</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0003917212134551788</v>
+        <v>0.0002028766487174186</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0003743239219617285</v>
+        <v>0.0007643086139106926</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.003456764792317899</v>
+        <v>0.002392291039381486</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.001051611465501395</v>
+        <v>0.001353255494881604</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0007328705005815382</v>
+        <v>0.0005055054591962467</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001224251209257184</v>
+        <v>0.002513661835113709</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.001676419551876726</v>
+        <v>0.001541688744513155</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0004272587299519881</v>
+        <v>0.0006406368968591041</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001138873367155042</v>
+        <v>0.0006280174096443624</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.003025772437221235</v>
+        <v>0.003451163496591347</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0009898023594909473</v>
+        <v>0.001075750483487756</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.002842694617764683</v>
+        <v>0.001253977084858136</v>
       </c>
       <c r="EE4" t="n">
-        <v>6.868186504128379e-05</v>
+        <v>0.0001314986974542179</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.002061116298185039</v>
+        <v>0.0009746739930025169</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001401080469166619</v>
+        <v>0.003623965002359726</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0006636139991105728</v>
+        <v>0.0003699612085349321</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001702780416251858</v>
+        <v>0.0009024729986666525</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0009183252952365783</v>
+        <v>0.00107960756273284</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001189759071294047</v>
+        <v>0.001061949266851159</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0001552579493079531</v>
+        <v>0.0001074667977501203</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0002113403441250733</v>
+        <v>0.000321598302911737</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0004354107831643309</v>
+        <v>0.0002169475368691425</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0002612163975272768</v>
+        <v>0.0002005638331986044</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.00122458870646593</v>
+        <v>0.002727385405646925</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0008758301534666969</v>
+        <v>0.0003417697785324115</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0007293062100281153</v>
+        <v>0.00037161885837078</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001722893707023916</v>
+        <v>0.001288128900004919</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001774772675286159</v>
+        <v>0.001169710945635681</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0007401812693267464</v>
+        <v>8.13280984874248e-05</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0007111089268436001</v>
+        <v>0.001132836650500672</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0006596618105565589</v>
+        <v>0.001915724843933807</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001241852429466407</v>
+        <v>0.0005051017476275574</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.008086143843965821</v>
+        <v>-0.003616416091019914</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.001210464662241273</v>
+        <v>-0.003273185060847639</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.000812677773262882</v>
+        <v>-0.0007314099959365939</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001761006289308142</v>
+        <v>-0.00345388053636736</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.000718512256973769</v>
+        <v>-0.0006708595387841076</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.00531197301854972</v>
+        <v>-0.002153596099146659</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.002096436058700179</v>
+        <v>-0.002108551347130039</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.00914813260595888</v>
+        <v>-0.007007973143096901</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.002559798573227057</v>
+        <v>-0.004402515723270484</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0008853288364249479</v>
+        <v>-0.002928543537680617</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.003397110503709455</v>
+        <v>-0.004754164973587971</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.005101180438448527</v>
+        <v>-0.002303787582975403</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01959714645404954</v>
+        <v>-0.008644565673520732</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.002112962210483493</v>
+        <v>-0.004347826086956519</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002303787582975403</v>
+        <v>-0.001841473178542796</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.005786163522012544</v>
+        <v>-0.004679512386944506</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.001183431952662695</v>
+        <v>-0.002138364779874269</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01420741989881954</v>
+        <v>-0.01741502308015106</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.00452948067161264</v>
+        <v>-0.001886792452830233</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.003035413153456978</v>
+        <v>-0.005870020964360623</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.008898821617228747</v>
+        <v>-0.009711499390491651</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.00366208905534745</v>
+        <v>-0.00312377977352597</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.006638032018742667</v>
+        <v>-0.005700898086684903</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.001022414471097133</v>
+        <v>-0.001342845153168237</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.006028667790893738</v>
+        <v>-0.004606931530008429</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.01184654300168633</v>
+        <v>-0.008208045509955308</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.003748535728231128</v>
+        <v>-0.0005044136191676874</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.01064989517819704</v>
+        <v>-0.001686340640809392</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.01194968553459116</v>
+        <v>-0.008368554522400618</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.03157253149126368</v>
+        <v>-0.02043884599756193</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.006424344885883326</v>
+        <v>-0.005770012190166573</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0009232060428032374</v>
+        <v>-0.001479289940828343</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.002030456852791862</v>
+        <v>-0.00811265237494745</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.00172052035249689</v>
+        <v>-0.004632263307598539</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.0206826493295408</v>
+        <v>-0.01300284437220641</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.005367709213863048</v>
+        <v>-0.01031276415891795</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.004724716907457982</v>
+        <v>-0.00166598943518893</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.002842273819055241</v>
+        <v>0.000336275746111836</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.003273185060847694</v>
+        <v>-0.004245481294661568</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01119496855345908</v>
+        <v>-0.006663957740755766</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.002578191039729494</v>
+        <v>-0.001593291404612207</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.003920741989881927</v>
+        <v>-0.003614964270701926</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.02494920763917103</v>
+        <v>-0.02389272653392929</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.002205576362879702</v>
+        <v>-0.002694260054666164</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01016020236087689</v>
+        <v>-0.00176100628930822</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.004510961214165244</v>
+        <v>-0.003475204998047643</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.002155536770921384</v>
+        <v>-0.004737945492662499</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.004932546374367608</v>
+        <v>-0.002935010482180333</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.002356765542462358</v>
+        <v>-0.001635220125786208</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.004318658280922394</v>
+        <v>-0.00512820512820511</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.002515723270440207</v>
+        <v>-0.0002401921537229734</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.009862671660424449</v>
+        <v>-0.0007078254030671971</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.001706623323852052</v>
+        <v>-0.005170239596469062</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0007418976962123902</v>
+        <v>-0.0004403522818254513</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001706200582605055</v>
+        <v>-0.0006638032018742912</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.008846960167714834</v>
+        <v>-0.005995807127882657</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.002663337494798146</v>
+        <v>-0.00251930109711499</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.006112984822934197</v>
+        <v>-0.004448174569869867</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.004451386177274474</v>
+        <v>-0.002690205968894444</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.003145890680298879</v>
+        <v>-0.002012578616352234</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.001730239874164385</v>
+        <v>-0.00747663551401867</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.007040472175379398</v>
+        <v>-0.00906420478388581</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.000873907615480618</v>
+        <v>-0.002225693088637259</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.003396226415094294</v>
+        <v>-0.004835432750914248</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.008863920099875133</v>
+        <v>-0.0008199921905505559</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.005935181569699299</v>
+        <v>-0.006457023060796685</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.005700898086684869</v>
+        <v>-0.003689727463312431</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.00230378758297538</v>
+        <v>-0.002069504099960962</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.005241090146750482</v>
+        <v>-0.008938313050776293</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001349072512647553</v>
+        <v>-0.0005466614603670706</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.003002401921537245</v>
+        <v>-0.002900378310214335</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.00206576728499156</v>
+        <v>-0.007127882599580748</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0003372681281618384</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.003119730185497449</v>
+        <v>-0.01053294167016361</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.005480607082630673</v>
+        <v>-0.009415720891130686</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.008099034830046203</v>
+        <v>-0.006179066834804514</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.004119850187265894</v>
+        <v>-0.0005466614603670483</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.002976939203354245</v>
+        <v>-0.001950426655830939</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.00251572327044024</v>
+        <v>-0.001991060544494083</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.004997968305566802</v>
+        <v>-0.003846153846153799</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.006834381551362656</v>
+        <v>-0.008846960167714923</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.001306913996627301</v>
+        <v>-0.006809583858764146</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.003826630222569283</v>
+        <v>-0.008015107007973133</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002162799842705465</v>
+        <v>-0.001572945340149379</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.005450733752620518</v>
+        <v>-0.007763323541754052</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.0002098195551825666</v>
+        <v>-0.0003745318352059379</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.002958579881656798</v>
+        <v>-0.005674653215636816</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.009527528309254185</v>
+        <v>-0.001723413198822998</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.0002958579881656487</v>
+        <v>-0.003186582809224359</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.005544709098008571</v>
+        <v>-0.002473794549266284</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.001679031628270167</v>
+        <v>-0.003102725366876324</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0001171417415072318</v>
+        <v>-0.0003932363350372947</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.003279968762202246</v>
+        <v>-0.001928721174004233</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.003480083857442307</v>
+        <v>-0.004654088050314508</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.001955888472742395</v>
+        <v>-0.001345102984447188</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.002065767284991571</v>
+        <v>-0.001133025597985682</v>
       </c>
       <c r="CU5" t="n">
+        <v>-0.001828524989841496</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-0.001600937133932068</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>-0.001849516603614931</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>-0.004099960952752823</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>-0.001048218029350134</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.0002529510961213899</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>-0.0008010118043844328</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-0.001690617075232415</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0.0006708595387840965</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>-0.004696016771488521</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0.01295597484276734</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-0.002925639983746453</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0.007650273224043691</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0.0106918238993711</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0.002895509861519063</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0.006213017751479244</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>-4.06338886631441e-05</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>-0.002577118313158921</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0.00466582597730133</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0.01115807269653419</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0.005660377358490587</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0.0003794266441820682</v>
+      </c>
+      <c r="DR5" t="n">
         <v>-0.0002438033319788646</v>
       </c>
-      <c r="CV5" t="n">
-        <v>-0.0002107925801011379</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>-0.003037869330004117</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>-0.004568527918781684</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>-0.0004161464835621742</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>-0.0002535925612848322</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>-0.00108086469175338</v>
-      </c>
-      <c r="DC5" t="n">
-        <v>-0.00960562280359234</v>
-      </c>
-      <c r="DD5" t="n">
-        <v>-0.0004718836020448647</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>-0.0007809449433814674</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>-0.0009437672040896628</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>-0.002431865828092183</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>-0.003372681281618872</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>-0.002663337494798146</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>-0.009340659340659318</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>-0.002451394759087055</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>-0.0002001601281024779</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>-0.004322282836760427</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>-0.01077568134171905</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>-0.00746957616449857</v>
-      </c>
-      <c r="DP5" t="n">
-        <v>-0.00646244229962234</v>
-      </c>
-      <c r="DQ5" t="n">
-        <v>-0.001352493660185927</v>
-      </c>
-      <c r="DR5" t="n">
-        <v>-0.000211327134404038</v>
-      </c>
       <c r="DS5" t="n">
-        <v>-0.0001248439450686423</v>
+        <v>-0.001563820794589998</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.009651699538397007</v>
+        <v>-0.006924045321023886</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.001901944209636508</v>
+        <v>-0.002655212807497065</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.001835220616946498</v>
+        <v>-0.001132370167903174</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.0004876066639577292</v>
+        <v>-0.006255283178360038</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.004363490792634128</v>
+        <v>-0.001048218029350156</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0009571369121930684</v>
+        <v>-0.001137748882568035</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.001225697379543511</v>
+        <v>-0.000780944943381523</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.008770457406630327</v>
+        <v>-0.008308854385228669</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.002201761409127278</v>
+        <v>-0.001747257212515208</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.002655212807497054</v>
+        <v>-0.002069504099960972</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0.0003803888419272483</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.005031446540880458</v>
+        <v>-0.001563820794589965</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.002782462057335588</v>
+        <v>-0.01162299239222312</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.001970649895178156</v>
+        <v>-0.000461215932914083</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.004737945492662421</v>
+        <v>-0.001433389544687969</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.001593291404612107</v>
+        <v>-0.00224006762468294</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.002028740490278946</v>
+        <v>-0.001559865092748691</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0.0004161464835621409</v>
+        <v>-4.06338886631441e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0004161464835621853</v>
+        <v>-0.0007028504490433462</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0004577611319183772</v>
+        <v>-0.0001200960768614867</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0006294586655476552</v>
+        <v>-0.0003803888419272483</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.003677092138630589</v>
+        <v>-0.00824175824175819</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.002769618128409579</v>
+        <v>-0.001007133864876164</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.002318718381112983</v>
+        <v>-0.0004192872117400936</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.003682946357085703</v>
+        <v>-0.002844372206420154</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.003857442348008333</v>
+        <v>-0.003169907016060813</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.001000800640512389</v>
+        <v>-0.0001625355546525764</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.0008853288364249256</v>
+        <v>-0.003144654088050369</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.00144115292233784</v>
+        <v>-0.002722470540430733</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.003414839797639091</v>
+        <v>-0.0005494505494505142</v>
       </c>
     </row>
     <row r="6">
@@ -3083,298 +3083,298 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0005074572163653313</v>
+        <v>-0.001265468080995061</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0002175902394299683</v>
+        <v>-0.0005926928346176642</v>
       </c>
       <c r="D6" t="n">
-        <v>-8.484865464039315e-05</v>
+        <v>-0.0004220768722659835</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0002935065930092934</v>
+        <v>-0.0005071141152059006</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0006383922612457322</v>
+        <v>-0.0002418379492397426</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.002965659877022594</v>
+        <v>-0.000686347818369315</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001315743904600664</v>
+        <v>-0.0003288326664713931</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.004319064841034967</v>
+        <v>-0.001701364930563792</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001647479773848062</v>
+        <v>-0.0009914751375282999</v>
       </c>
       <c r="K6" t="n">
-        <v>9.830908375932368e-06</v>
+        <v>-0.0005715887911356299</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0001711373302088537</v>
+        <v>-0.0001757126122608477</v>
       </c>
       <c r="M6" t="n">
-        <v>8.006405124099114e-05</v>
+        <v>-0.000942029527726182</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003481302022238711</v>
+        <v>-0.001992705781284815</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0005982892823134078</v>
+        <v>-0.001459608143404731</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0008772115830955801</v>
+        <v>-0.0008778909302060405</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.003323645939952921</v>
+        <v>0.001637805317806257</v>
       </c>
       <c r="R6" t="n">
-        <v>-3.121098626716057e-05</v>
+        <v>-0.0003852696134965583</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.005877549375127964</v>
+        <v>-0.001810988935735322</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0005844124314143079</v>
+        <v>-0.0004701449115070672</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.001497772897360353</v>
+        <v>-0.0007852980281523842</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.001391351925245862</v>
+        <v>-0.001266688430706081</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001212389494765295</v>
+        <v>-0.001306512143908181</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0005706187921622835</v>
+        <v>-0.000511779989261657</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0.0006352150387683275</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.001217512513775162</v>
+        <v>-0.001090282356405348</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.001837871205331804</v>
+        <v>-0.0015032123295417</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.001057540876318944</v>
+        <v>-0.0001095574333934951</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.000787447372083533</v>
+        <v>-0.001002906139379431</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.003515119788138182</v>
+        <v>-0.0004548784046152026</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0004763071172628141</v>
+        <v>0.002895231306955737</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0007383008195646024</v>
+        <v>-0.000861229653154949</v>
       </c>
       <c r="AG6" t="n">
-        <v>-9.509721048181209e-05</v>
+        <v>-0.0003738047184279391</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0008300372493654895</v>
+        <v>0.0007165524039858761</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.0002853718145908845</v>
+        <v>-0.0002738479932678534</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.0001494438337886039</v>
+        <v>-0.001101842892278132</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.001951851042403696</v>
+        <v>0.002477034945407269</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.001010262626484088</v>
+        <v>-0.0009675760913299025</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.001955503909534992</v>
+        <v>0.002916453725018359</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001243284667268527</v>
+        <v>-0.001780729935672493</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.00313142314358669</v>
+        <v>-0.003579629779706414</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.001243716701353287</v>
+        <v>-0.0004766958629886325</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.001958050468209932</v>
+        <v>-0.002224083998781335</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.001360853671873349</v>
+        <v>-0.003682461926471972</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0001312601514601081</v>
+        <v>-0.0005947894339591392</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.005579615210878117</v>
+        <v>-0.001122501669643222</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.001103511822054123</v>
+        <v>-0.00099379629807248</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0002858378002428497</v>
+        <v>-0.0001244428190474933</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.00197277162475745</v>
+        <v>-0.0002237873191686169</v>
       </c>
       <c r="AX6" t="n">
-        <v>-8.420546449930122e-05</v>
+        <v>-0.0005734767436201716</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.002692298447906935</v>
+        <v>-0.0004954357027238537</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-1.69562223973796e-05</v>
+        <v>2.498001805406602e-17</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.0009140388296008384</v>
+        <v>0.0003355945201299587</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.0006832051755989109</v>
+        <v>-0.0003682133953512051</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0001248439450686367</v>
+        <v>2.775557561562892e-18</v>
       </c>
       <c r="BD6" t="n">
-        <v>-8.096684580496395e-05</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0006317750581793458</v>
+        <v>-0.0002298299512594665</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.001226239041992552</v>
+        <v>0.0007274706903388995</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.000636298209675476</v>
+        <v>-0.0006831723485047376</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0003377025329129396</v>
+        <v>-0.0001998059320440948</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.001042701623191938</v>
+        <v>0.001197978138711056</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0008361821865969482</v>
+        <v>-0.0006274797319645281</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.001302727074464047</v>
+        <v>-0.002755086183793343</v>
       </c>
       <c r="BL6" t="n">
-        <v>-1.835156159246675e-05</v>
+        <v>-0.0007330558042465823</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0006686535738139321</v>
+        <v>-0.00120619741778204</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.002771387939443276</v>
+        <v>0.0005822240209750584</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.000623246693638535</v>
+        <v>-0.001695819799099765</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.0005161166977159792</v>
+        <v>-0.001192264593278136</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0008177684172743366</v>
+        <v>-0.0004187423867524826</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.003011124804165652</v>
+        <v>-0.001495298543256845</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0001034638671774085</v>
+        <v>-0.0003238673832198558</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.001229058835535132</v>
+        <v>-0.001103907426098827</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.0003423035315354983</v>
+        <v>-0.001138967436312202</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.00157464940676123</v>
+        <v>-0.001852502630376415</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001258597922852406</v>
+        <v>0.0002775677089056461</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.001053155465654454</v>
+        <v>-0.001146208340663593</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.002480775829454757</v>
+        <v>-8.526630210586029e-05</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.00122321170203514</v>
+        <v>-8.305995707307278e-05</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0004974290055508562</v>
+        <v>-0.0004535500238301737</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.002582242238236057</v>
+        <v>-0.002036939448475239</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.00205318430365736</v>
+        <v>-0.00337466935589959</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.000841850923961579</v>
+        <v>-0.001181269609945104</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.001318862730840831</v>
+        <v>-0.001618916255005296</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0004004707219656178</v>
+        <v>-0.0003945294600460531</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.001187327213203376</v>
+        <v>-0.001316325996445533</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.000755046104097537</v>
+        <v>-0.001041009764162062</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.001584173597766198</v>
+        <v>-0.0009298151453984438</v>
       </c>
       <c r="CM6" t="n">
-        <v>-7.970985518261364e-05</v>
+        <v>-0.0003141566507643856</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0002084822019648214</v>
+        <v>-0.0006113252100085342</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0001096108888238106</v>
+        <v>-0.001190171767155928</v>
       </c>
       <c r="CP6" t="n">
         <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0007945626018616813</v>
+        <v>-0.001358940068369113</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.00115744910826881</v>
+        <v>-0.001773109748509966</v>
       </c>
       <c r="CS6" t="n">
-        <v>-2.602334074072455e-05</v>
+        <v>-0.0005300398932964273</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.0004250220066941424</v>
+        <v>-0.0009390149785190788</v>
       </c>
       <c r="CU6" t="n">
-        <v>-6.004803843074336e-05</v>
+        <v>0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
@@ -3383,130 +3383,130 @@
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>8.203009100485603e-05</v>
+        <v>-0.000862162073263656</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.001469078394614315</v>
+        <v>-0.001062867948835708</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0001779001101614247</v>
+        <v>-0.0005376774657875755</v>
       </c>
       <c r="DA6" t="n">
-        <v>0</v>
+        <v>-0.0001884616451480137</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.0002465081577426365</v>
+        <v>-0.0001359343131678542</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.0008768989237792207</v>
+        <v>-0.0004352276616347351</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.775557561562892e-18</v>
+        <v>-0.0002206698374609822</v>
       </c>
       <c r="DE6" t="n">
-        <v>-6.952507926065721e-05</v>
+        <v>-0.0002738752944361822</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0003302642113690829</v>
+        <v>-0.000768188020637689</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0006887928054058606</v>
+        <v>-0.001528517826941148</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.0006569724570923835</v>
+        <v>-0.002278757768598127</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0001051052168869193</v>
+        <v>-0.001749516545393034</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0007789327765512638</v>
+        <v>-0.0007296044068086482</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.001348985971965219</v>
+        <v>-0.0002702161729383534</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-2.928543537680794e-05</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.002161130144540649</v>
+        <v>-0.000252765024486995</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.001912749802838426</v>
+        <v>-0.002871266055826943</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.001951075086569015</v>
+        <v>-0.004593952506708252</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.001967557807116418</v>
+        <v>-0.001403440969760047</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-9.363295880147338e-05</v>
+        <v>-0.0001574852336826554</v>
       </c>
       <c r="DR6" t="n">
-        <v>-1.973091333553611e-05</v>
+        <v>-6.294586655475332e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0.0003579452451910714</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.0006321199294368641</v>
+        <v>-0.001402965445331686</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.0007497541242412586</v>
+        <v>-0.001985387774584446</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.0007782331555736515</v>
+        <v>-0.000155596129919719</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0002664971143253647</v>
+        <v>-0.001299268986664434</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.001936792575620242</v>
+        <v>-0.0002993364901334339</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.0001219016659894351</v>
+        <v>-0.0001769563507667826</v>
       </c>
       <c r="EA6" t="n">
-        <v>3.14581078669135e-05</v>
+        <v>-0.0004491596990774754</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.00490699878928972</v>
+        <v>-0.003763363968981151</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0002867341618513653</v>
+        <v>-0.0001050597338874498</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.001838996399245177</v>
+        <v>-0.0009791744931625268</v>
       </c>
       <c r="EE6" t="n">
         <v>0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.001243851643687943</v>
+        <v>-0.0001264463915069958</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0005657269579622092</v>
+        <v>-0.0009170551140028737</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0.0001285372572314147</v>
+        <v>-0.0003225543686468685</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.002167146150890622</v>
+        <v>-0.001100901879978528</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0002191148667870485</v>
+        <v>-0.0004786051641558403</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.001396753942422088</v>
+        <v>-0.001470589013498785</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.0002622843021837324</v>
+        <v>-0.0001195647827739121</v>
       </c>
       <c r="EN6" t="n">
         <v>0</v>
@@ -3515,10 +3515,10 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.0002317243995001634</v>
+        <v>-0.0001710844566638642</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.001145737639271624</v>
+        <v>-0.000364967812932418</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
@@ -3527,22 +3527,22 @@
         <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0003880134052704071</v>
+        <v>-0.0005352515373978517</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.001754323511381295</v>
+        <v>-0.0002506641550857586</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0.0001267160974969844</v>
+        <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0005583612305302354</v>
+        <v>-0.001585499876514268</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.00101092866205888</v>
+        <v>-0.001214033969393313</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0001783290269739141</v>
+        <v>-0.0003427181110374183</v>
       </c>
     </row>
     <row r="7">
@@ -3552,295 +3552,295 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0001263686372001527</v>
+        <v>6.949205937856412e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0002528996854343713</v>
+        <v>-0.0001011433092510949</v>
       </c>
       <c r="D7" t="n">
-        <v>8.441537445320614e-05</v>
+        <v>-8.322929671242817e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>4.373632356934888e-05</v>
+        <v>-0.0001888375996642711</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0003421124157382216</v>
+        <v>0.0001463497946073922</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0006196376956383253</v>
+        <v>-0.0003492832096698651</v>
       </c>
       <c r="H7" t="n">
-        <v>-6.292765463972172e-05</v>
+        <v>-0.0001040849493381901</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.00101408692821342</v>
+        <v>-0.0005131592626546111</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.000322607620013593</v>
+        <v>-0.0005186537663990742</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001612448031121538</v>
+        <v>-0.0001632933479534193</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002424930768194611</v>
+        <v>1.966181675187029e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0003865999566368405</v>
+        <v>5.421669520527805e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.001509014969142236</v>
+        <v>0.0003002401921537223</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0002949235405072692</v>
+        <v>-0.0007127841478845376</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0004221923515744518</v>
+        <v>-0.0001757126122608366</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003142538419965912</v>
+        <v>0.003284067120529566</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0006950572994307235</v>
+        <v>6.356747996059675e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>1.116700630159339e-05</v>
+        <v>-0.0004081459262186337</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0001885674746521349</v>
+        <v>-9.966450113943481e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0008140928056635577</v>
+        <v>0.0001087735484233299</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.00025217153097018</v>
+        <v>-0.0005523018493441778</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0002501059401826378</v>
+        <v>0.0007964870816711155</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002045700229165615</v>
+        <v>0.001553272883123657</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.31137262741055e-05</v>
+        <v>-0.0003262635328943997</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000569197511189945</v>
+        <v>0.000261273382807331</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0003860992256891071</v>
+        <v>0.0007165124114804466</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.000104560514910973</v>
+        <v>4.308119598965267e-05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0002986876815029238</v>
+        <v>-0.000819237038420656</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.002422821307506756</v>
+        <v>0.004434799271915518</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.006032954056680756</v>
+        <v>0.00443739146999419</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001057853428602457</v>
+        <v>0.0005907537785862282</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001254031149915069</v>
+        <v>-0.0002938217059393733</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0002925949117303261</v>
+        <v>0.001224743949786905</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0003507822319486764</v>
+        <v>0.000146490909062319</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001110064154408247</v>
+        <v>0.001869515789176124</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.004279587194863266</v>
+        <v>0.007236890498011189</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0003037526314092376</v>
+        <v>-0.000256959035154386</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0001904616981150742</v>
+        <v>0.004659759804690794</v>
       </c>
       <c r="AN7" t="n">
-        <v>-8.406893652797565e-05</v>
+        <v>0.0003152158452331743</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0009422826270569118</v>
+        <v>-0.0005667107326261689</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0002230570711711843</v>
+        <v>0.000129738074019542</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.0006545070897457317</v>
+        <v>-0.0004789675232124146</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.002732223609909335</v>
+        <v>0.001450254943548435</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0003730469199478226</v>
+        <v>8.45308537616496e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.001748914485823505</v>
+        <v>5.756866602210089e-05</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.0004277897483303816</v>
+        <v>-6.279510863258508e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0002321437719433328</v>
+        <v>0.0001630220711461849</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0003566932438103187</v>
+        <v>0.0001044564407983506</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.001601281022558e-05</v>
+        <v>-0.0002678023741953417</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.001251445513469357</v>
+        <v>0.0007857745203028454</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0006465310403544422</v>
+        <v>0.0003997435885137291</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.0005033125923049886</v>
+        <v>0.001545619467888787</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0004256524950145557</v>
+        <v>0.004832732500506698</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.031694433157205e-05</v>
+        <v>0.0001886792452830133</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.665334536937735e-17</v>
+        <v>0.0001049097775912944</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0003963887091534779</v>
+        <v>0.001344750198309941</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0002912376138825945</v>
+        <v>0.005435208200287078</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.00133038572263745</v>
+        <v>0.0006216620471426403</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0001641675785723939</v>
+        <v>8.387503727926293e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.002270536461676487</v>
+        <v>0.004111189270602954</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0006325956515111475</v>
+        <v>0.0003333787686142676</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.000142384942833651</v>
+        <v>-0.0007379127807879027</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0004503644950428432</v>
+        <v>-0.0001651342090906782</v>
       </c>
       <c r="BM7" t="n">
-        <v>-1.069108605589229e-07</v>
+        <v>-0.0004617097069537779</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0008260732926040292</v>
+        <v>0.0008063666249396751</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0001000800640512167</v>
+        <v>-0.0003709219966325949</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0001053962900506078</v>
+        <v>-0.0004845748387201698</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.000309340058031532</v>
+        <v>0.0004189740991784263</v>
       </c>
       <c r="BS7" t="n">
-        <v>3.588711122499145e-05</v>
+        <v>-0.0006455185165366196</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.226542688082202e-05</v>
+        <v>-0.0001469089672414936</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.0005224075681816542</v>
+        <v>6.339814032123581e-05</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.0002064944992491435</v>
+        <v>-0.0005905239465059331</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.0002185825891818927</v>
+        <v>-6.289308176102293e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0004108870952998111</v>
+        <v>0.0007147502602488587</v>
       </c>
       <c r="BZ7" t="n">
-        <v>7.750175958121663e-05</v>
+        <v>0.0002233413863841904</v>
       </c>
       <c r="CA7" t="n">
-        <v>-9.900004959599308e-05</v>
+        <v>0.0001888728782780624</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.0004767516491849922</v>
+        <v>6.294586655476442e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0001234262933465402</v>
+        <v>-0.0001187508313630903</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.0008125218555957714</v>
+        <v>0.0003138551450297233</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0008289931554395392</v>
+        <v>-0.0001200960768614701</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0003591274280830947</v>
+        <v>-0.0001373563309283954</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0004628753419288034</v>
+        <v>-0.000377349908040453</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0001052102184162129</v>
+        <v>-2.15657704693839e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.0001202530103583788</v>
+        <v>-0.0005163270858942858</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0001102298670847268</v>
+        <v>0.0009018897835911532</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.000392861498598801</v>
+        <v>-0.0006927681350742954</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0003905958243711705</v>
+        <v>2.101723413200363e-05</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0002320322044021828</v>
+        <v>4.196391103652442e-05</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0001401120896717234</v>
+        <v>-0.0004364324988057999</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>2.101723413200918e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0005716756004857161</v>
+        <v>-0.0009983941601438449</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.0004718836020448425</v>
+        <v>-0.0005354736010593552</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0005909141448770583</v>
+        <v>0.0002569426631753802</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.203726097331217e-05</v>
+        <v>-0.00077301172276793</v>
       </c>
       <c r="CU7" t="n">
         <v>0</v>
@@ -3852,133 +3852,133 @@
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0003159353961510181</v>
+        <v>0.0001446659176475184</v>
       </c>
       <c r="CY7" t="n">
-        <v>-0.0004008707768431041</v>
+        <v>-0.0004300599557521989</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.966181675185919e-05</v>
+        <v>-4.003202562049557e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>6.215003870235769e-05</v>
+        <v>7.907927278956728e-05</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0008448996442015466</v>
+        <v>0.0007766145830853278</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0001422186103210265</v>
+        <v>-4.209649214210188e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>6.095083299472171e-05</v>
+        <v>-0.0001220279622774767</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0003826155035759338</v>
+        <v>-0.0003735745182854688</v>
       </c>
       <c r="DG7" t="n">
-        <v>-2.372806889225919e-05</v>
+        <v>-0.0008935837020646708</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.0003791827785500967</v>
+        <v>-0.0008483009004167597</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0001261034047919218</v>
+        <v>-0.0006681773470489316</v>
       </c>
       <c r="DJ7" t="n">
-        <v>5.551115123125783e-18</v>
+        <v>-0.0003793495281515124</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0.0004030632487329267</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>4.133417846355903e-05</v>
+        <v>2.101723413199252e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0004388923675954948</v>
+        <v>-0.0001415931335622067</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.0002598559415490309</v>
+        <v>-0.001118078273748813</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.061787585290187e-05</v>
+        <v>-0.0015120673063587</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.0001391108683499953</v>
+        <v>-6.004803843074335e-05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0</v>
+        <v>-2.031694433157205e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.197992384674999e-05</v>
+        <v>1.952362358453863e-05</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-1.952362358453863e-05</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0006431307804866338</v>
+        <v>-0.0003762093449745152</v>
       </c>
       <c r="DU7" t="n">
-        <v>2.12649039975642e-06</v>
+        <v>-0.0007423884600342822</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>2.080732417812925e-05</v>
+        <v>-8.164667397670967e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0001049621229036901</v>
+        <v>-0.0002074615065596253</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.001114908042988361</v>
+        <v>0.001047896749333166</v>
       </c>
       <c r="DZ7" t="n">
-        <v>6.305170239596092e-05</v>
+        <v>2.09819555182622e-05</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0002719645839925899</v>
+        <v>4.22558185121269e-05</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.001792789650391008</v>
+        <v>-0.0001663471230452907</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.606002607416392e-05</v>
+        <v>0.0001787273310587201</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0.000599831564602521</v>
+        <v>-0.0001250581068024448</v>
       </c>
       <c r="EE7" t="n">
         <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.0001797912332833107</v>
+        <v>0.0001622545928817498</v>
       </c>
       <c r="EG7" t="n">
-        <v>2.03169443315665e-05</v>
+        <v>-0.0005048681154347923</v>
       </c>
       <c r="EH7" t="n">
-        <v>-2.080732417810705e-05</v>
+        <v>-4.226542688080537e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.0005886194221614183</v>
+        <v>-0.0002929925469353944</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0001015847216578603</v>
+        <v>-6.104925975248255e-05</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0.0002962826686581599</v>
+        <v>-0.0009697868184657342</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-2.001601281024779e-05</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>1.952362358453863e-05</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.0003900120094199766</v>
+        <v>-0.000136665365091776</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
@@ -3996,22 +3996,22 @@
         <v>0</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.0001187283830012709</v>
+        <v>-0.0003378102716456666</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0004834492950309355</v>
+        <v>-0.0001245715943431091</v>
       </c>
       <c r="EV7" t="n">
-        <v>-4.196391103651331e-05</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0002886389594445093</v>
+        <v>-0.0009139530998294121</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0.0004215494006174159</v>
+        <v>-0.0001996677388767742</v>
       </c>
       <c r="EY7" t="n">
-        <v>0</v>
+        <v>-0.0001472628985952129</v>
       </c>
     </row>
     <row r="8">
@@ -4021,298 +4021,298 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00207221224070237</v>
+        <v>0.003504992673383964</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009560732933807963</v>
+        <v>6.242197253433779e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005762923786621687</v>
+        <v>0.0003602882305844601</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0006177107472243815</v>
+        <v>0.0004356605014196907</v>
       </c>
       <c r="F8" t="n">
-        <v>-9.233713777280218e-05</v>
+        <v>0.0002907370032217887</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0008756475227384209</v>
+        <v>0.0007969650470134065</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0007117239596539205</v>
+        <v>0.0006506994601588629</v>
       </c>
       <c r="I8" t="n">
-        <v>4.19189889555388e-05</v>
+        <v>0.001086593765591967</v>
       </c>
       <c r="J8" t="n">
-        <v>7.413284989484515e-05</v>
+        <v>-4.226542688080537e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000585306535514718</v>
+        <v>-2.098195551824278e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006099388131333956</v>
+        <v>0.0002001169841801653</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0006051789878868341</v>
+        <v>0.001675950068708743</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0008500401500352889</v>
+        <v>0.00312496987570347</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001092757612287867</v>
+        <v>0.001864984343341347</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00025319949046613</v>
+        <v>0.0005477505888724727</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.004851856248360831</v>
+        <v>0.005265625505222029</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001562615800193742</v>
+        <v>0.001007812275525943</v>
       </c>
       <c r="S8" t="n">
-        <v>0.002849552000227804</v>
+        <v>0.0005738064669825544</v>
       </c>
       <c r="T8" t="n">
-        <v>-5.11347500292747e-05</v>
+        <v>0.0008269351528222113</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0001050861706599543</v>
+        <v>0.00146984485791751</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002661435345199412</v>
+        <v>0.001615930929882209</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0006717052308072097</v>
+        <v>0.002453123547527189</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001674605588902359</v>
+        <v>0.004058916582971065</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0003076587450689811</v>
+        <v>-3.161888701517235e-05</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002330561911035295</v>
+        <v>0.001715929547633138</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0009243017600394365</v>
+        <v>0.001359667615749455</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0001576292559899023</v>
+        <v>0.001293397407867297</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0008425500816234194</v>
+        <v>-0.0005435935427292066</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.007997944914053831</v>
+        <v>0.0157626757043814</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.00866354184015799</v>
+        <v>0.01136467166538661</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003296374013795022</v>
+        <v>0.00110188613269766</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0003730362795586723</v>
+        <v>0.0008378341246549458</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0008079247417909413</v>
+        <v>0.001679102103153118</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0008074733747264167</v>
+        <v>0.001409719503780474</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002587853926268394</v>
+        <v>0.002773049634243424</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01071066527265588</v>
+        <v>0.01500590956445851</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0001267331346535561</v>
+        <v>0.0004112058974882149</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.004484615120247646</v>
+        <v>0.006468117158144771</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001710717547878454</v>
+        <v>0.003363664714543183</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0002265895511067401</v>
+        <v>0.0008797201695783102</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001050241542306377</v>
+        <v>0.0009372741828074793</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001289326478481575</v>
+        <v>0.0007744957838324379</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.004718904828084425</v>
+        <v>0.004704204478855676</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001069958584313238</v>
+        <v>0.001321616447654467</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0003933159137650439</v>
+        <v>0.001421133477505043</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0004329319272572907</v>
+        <v>0.0008178387386198971</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0007661240306393758</v>
+        <v>0.001202078988594812</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0008643435932070953</v>
+        <v>0.0007816422156523728</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0002294994360967501</v>
+        <v>-2.001601281024779e-05</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.0003906770206066362</v>
+        <v>0.001554844890282508</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.001020606127793994</v>
+        <v>0.00246715854969965</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.00270530210407052</v>
+        <v>0.005207952231906896</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.006022501512544484</v>
+        <v>0.008699483466072164</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0001881184542912834</v>
+        <v>0.0006342351122743395</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.323777403037799e-05</v>
+        <v>0.0003540736152863461</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0006951679681974354</v>
+        <v>0.00242876529359867</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.007229806877451581</v>
+        <v>0.007628642642616307</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.00220949491742152</v>
+        <v>0.001225250853294543</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0004477312441644288</v>
+        <v>0.0008962961088723881</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.006507607812009869</v>
+        <v>0.005828513341003353</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001057802216616075</v>
+        <v>0.0008230451397597483</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001024078420603231</v>
+        <v>0.0008097673818069835</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.001032202525052728</v>
+        <v>0.0001263081967490281</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0004586007717339413</v>
+        <v>-0.0002096649509143955</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001772722863517312</v>
+        <v>0.003435853265206059</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001681399790572627</v>
+        <v>0.0003130177883463647</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0003637967120228153</v>
+        <v>-1.95236235845414e-05</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001593903154432774</v>
+        <v>0.001210575573151257</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0004429049676487912</v>
+        <v>4.14497953911519e-05</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0003645054408306731</v>
+        <v>0.0005944729907565227</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0003827910460181133</v>
+        <v>0.0005407011299346203</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0001464580973943114</v>
+        <v>-1.040366208904242e-05</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.9785831007641e-05</v>
+        <v>6.294586655478663e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0011534892574175</v>
+        <v>6.004803843074336e-05</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.00162638185647255</v>
+        <v>0.003171823058445089</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0004042287084105145</v>
+        <v>0.001122070538508352</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0003783144844355601</v>
+        <v>0.0009716137454283319</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.355897726814716e-05</v>
+        <v>0.0002732198369035766</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0003677134007754268</v>
+        <v>0.0002569590351544387</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0005621843414137406</v>
+        <v>0.001713744553428564</v>
       </c>
       <c r="CE8" t="n">
-        <v>9.742359361336606e-05</v>
+        <v>0.0008369553389109247</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0005570721838060789</v>
+        <v>8.460623272274758e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0001401543889380547</v>
+        <v>5.111992461878379e-05</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0002871152666154758</v>
+        <v>0.0008204722796551462</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0001374781166710609</v>
+        <v>-0.0002688416879710803</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.002284596126725663</v>
+        <v>0.00189565577974985</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0006662541936072936</v>
+        <v>0.0006136778583436392</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.00130824663768464</v>
+        <v>0.001309427458830206</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0005408651696017952</v>
+        <v>0.0001516219280594755</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001179954459377641</v>
+        <v>0.0007078446777397357</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0003775308367007457</v>
+        <v>0.000343808932832304</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.00313571726320177</v>
+        <v>9.901780438848485e-05</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0004398352248526777</v>
+        <v>0.0006724541965019453</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.00105695474402748</v>
+        <v>0.001199820313141498</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0004248417649630326</v>
+        <v>-0.0002065998548691383</v>
       </c>
       <c r="CU8" t="n">
-        <v>3.147293327737666e-05</v>
+        <v>4.123474506965429e-05</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
@@ -4321,166 +4321,166 @@
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.001012827916810088</v>
+        <v>0.0001989291550381994</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0001839029336847736</v>
+        <v>0.001099678226315362</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0</v>
+        <v>9.363295880150668e-05</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0001041725878065586</v>
+        <v>0.0001536007361500447</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0003453974390980274</v>
+        <v>0.0005914573425095853</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001078387817438275</v>
+        <v>0.001692121427754431</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0003633204507373977</v>
+        <v>6.004803843074336e-05</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0008814008855284494</v>
+        <v>2.949272512780543e-05</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0007654497661865296</v>
+        <v>0.0001478755386525837</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0003132804187117783</v>
+        <v>-0.0005214683665682784</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0004494574936666024</v>
+        <v>3.047541649735808e-05</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0006559468364815996</v>
+        <v>0.0004089193693099652</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0001148726738558065</v>
+        <v>8.785630613040719e-05</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0001993462167302395</v>
+        <v>0.000947024852453765</v>
       </c>
       <c r="DL8" t="n">
-        <v>7.296160153938969e-05</v>
+        <v>0.000239720806398655</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0001989860155638151</v>
+        <v>0.0003570415462344324</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0003037486735920719</v>
+        <v>-0.0003579432502047092</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0003365418996342295</v>
+        <v>7.351535967300982e-06</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.000501649868468082</v>
+        <v>0.0005566429693909331</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>9.441879983215496e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0002739683302534074</v>
+        <v>0.0002310838283619304</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>0.0002949272512780543</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0009065837588009967</v>
+        <v>0.00015809443507592</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0006006271041841399</v>
+        <v>6.239261207655332e-05</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>8.290909457127349e-05</v>
+        <v>-1.04821802935029e-05</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.001038469094420741</v>
+        <v>8.484865464041813e-05</v>
       </c>
       <c r="DY8" t="n">
-        <v>2.627367769486577e-05</v>
+        <v>0.001906637052836085</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0002922747296251499</v>
+        <v>0.0002009514394703454</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.000498901837327731</v>
+        <v>0.000581239622759236</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.0002503176199989576</v>
+        <v>0.000208230278190022</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0002745916361495792</v>
+        <v>0.0008327295454748252</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0.0001437320954736393</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>-8.326672684688674e-18</v>
+        <v>0.0007238246805860466</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0004205047123413019</v>
+        <v>-3.121098626715779e-05</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0001366340202265171</v>
+        <v>0.0002829751153368171</v>
       </c>
       <c r="EI8" t="n">
-        <v>-8.501893765504863e-05</v>
+        <v>0.000414563860826514</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0007419418681012202</v>
+        <v>0.0002200485859314955</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0005180820804551289</v>
+        <v>-0.0002142643389054372</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>9.441879983215496e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>3.047541649735808e-05</v>
+        <v>0.0002729575697645231</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>3.161888701518067e-05</v>
+        <v>0.0001081732504619959</v>
       </c>
       <c r="EQ8" t="n">
-        <v>-0.0001403993914603885</v>
+        <v>0.0004392340066590616</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0</v>
+        <v>0.0001269726498831669</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0003161888701517818</v>
+        <v>0.0002381387206220609</v>
       </c>
       <c r="EU8" t="n">
-        <v>-5.996814162516351e-05</v>
+        <v>0.0002928543537680433</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.000555270065821839</v>
+        <v>-0.000129572789179036</v>
       </c>
       <c r="EX8" t="n">
-        <v>-3.965119729359978e-05</v>
+        <v>0.0002845699831366177</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0001855435206367745</v>
+        <v>5.248941967191945e-05</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008073241781106976</v>
+        <v>0.006208512299882863</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001290054099042881</v>
+        <v>0.001341719077568104</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003144654088050347</v>
+        <v>0.003147293327738177</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001757126122608366</v>
+        <v>0.001498127340824007</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0008853288364249701</v>
+        <v>0.0004685669660288938</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002224087284934928</v>
+        <v>0.005157232704402481</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00257711831315891</v>
+        <v>0.002266051195971519</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002616165560327999</v>
+        <v>0.005035372451102804</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003783102143757544</v>
+        <v>0.0002031694433157205</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002976939203354312</v>
+        <v>0.0007720438845997379</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001886792452830222</v>
+        <v>0.001091061686949291</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001930339907679346</v>
+        <v>0.006163522012578582</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001310228233305177</v>
+        <v>0.007657095297544769</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00821802935010485</v>
+        <v>0.004947589098532457</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001914273824386181</v>
+        <v>0.0008385744234800541</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0176668065463701</v>
+        <v>0.01447754930759551</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00324092151503319</v>
+        <v>0.001981450252951134</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004841858648965258</v>
+        <v>0.006034124011652109</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0008006405124099114</v>
+        <v>0.001040366208905563</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001796173369777443</v>
+        <v>0.002698145025295162</v>
       </c>
       <c r="V9" t="n">
-        <v>0.004494382022471921</v>
+        <v>0.00690803162713276</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004947589098532523</v>
+        <v>0.004637436762226022</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01070826306914</v>
+        <v>0.008558178752107992</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0006004803843074336</v>
+        <v>0.000416146483562263</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0137106918238994</v>
+        <v>0.008553459119496832</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.00696600923206041</v>
+        <v>0.004490138480906447</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001180438448566634</v>
+        <v>0.00260176248426357</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.001706200582605077</v>
+        <v>-0.0002098195551824999</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01416561580496004</v>
+        <v>0.0174569869911876</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01483979763912312</v>
+        <v>0.02678142514011208</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.007337526205450762</v>
+        <v>0.004025157232704357</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.003288364249578446</v>
+        <v>0.001426772975241353</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001719077568134198</v>
+        <v>0.002641202763104456</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.006918238993710735</v>
+        <v>0.00342349957734579</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01148846960167719</v>
+        <v>0.01257861635220121</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02129703763010409</v>
+        <v>0.02963743676222602</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.004825849769198476</v>
+        <v>0.001955888472742429</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01644985312631133</v>
+        <v>0.01207547169811316</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.002306079664570271</v>
+        <v>0.004876066639577403</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.006155143338954483</v>
+        <v>0.02074198988195621</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.004192872117400459</v>
+        <v>0.003483004616030261</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00495174150230796</v>
+        <v>0.003776751993285798</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0128161888701518</v>
+        <v>0.02141652613827999</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.00188679245283021</v>
+        <v>0.002163961714523543</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0008257963035784299</v>
+        <v>0.002276559865092798</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.003773584905660421</v>
+        <v>0.004276729559748393</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.002473794549266284</v>
+        <v>0.002655212807497054</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.002683438155136297</v>
+        <v>0.003499156829679639</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.002725366876310331</v>
+        <v>0.0008010118043845438</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0001681378730558736</v>
+        <v>0.004402515723270406</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0137221989089383</v>
+        <v>0.01078472513638273</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0407127882599581</v>
+        <v>0.04482180293501044</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.02131766680654634</v>
+        <v>0.01363827108686533</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.000503566932438071</v>
+        <v>0.001306913996627379</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0002935010482180589</v>
+        <v>0.001914273824386226</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.005160503860219434</v>
+        <v>0.009446525176862276</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.02515723270440254</v>
+        <v>0.03329140461215928</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.02976939203354301</v>
+        <v>0.01589098532494755</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.002023608768971341</v>
+        <v>0.002356765542462425</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.02014267729752411</v>
+        <v>0.02719261435165762</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.003670441233893018</v>
+        <v>0.003246205733558216</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.004570230607966486</v>
+        <v>0.002642113690952785</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.002389937106918294</v>
+        <v>0.0009274873524452443</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0005874947545110865</v>
+        <v>0.001720520352496913</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.04083857442348011</v>
+        <v>0.04461215932914042</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.004089376053962912</v>
+        <v>0.004783885858162029</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.004737945492662499</v>
+        <v>0.0008739076154806846</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.006534569983136618</v>
+        <v>0.002012578616352179</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0006305170239596202</v>
+        <v>0.001944209636517402</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001828524989841585</v>
+        <v>0.00310272536687628</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.001299790356394159</v>
+        <v>0.002023608768971385</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.00137328339575532</v>
+        <v>0.002937473772555632</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.226542688081647e-05</v>
+        <v>0.0001264755480607338</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001483795392424847</v>
+        <v>0.0009761811792268537</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0125786163522013</v>
+        <v>0.004318658280922405</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.007463312368972774</v>
+        <v>0.009979035639412959</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.006498951781970685</v>
+        <v>0.00261382799325468</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002641202763104478</v>
+        <v>0.0009571369121931239</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.002455264253017053</v>
+        <v>0.0003773584905659933</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.008008385744234825</v>
+        <v>0.008595387840670821</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001261034047919252</v>
+        <v>0.002782462057335633</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.005371380612673083</v>
+        <v>0.004989517819706457</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0007314099959366604</v>
+        <v>0.002054507337526168</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.00335429769392035</v>
+        <v>0.001310228233305222</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.000609508329947206</v>
+        <v>0.001498127340824018</v>
       </c>
       <c r="CJ9" t="n">
-        <v>4.226542688081647e-05</v>
+        <v>0.0001677148846960019</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.006492411467116377</v>
+        <v>0.003329171868497727</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.001462819991873299</v>
+        <v>0.002096436058700157</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002663337494798157</v>
+        <v>0.002372034956304647</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0009571369121930795</v>
+        <v>0.005035372451102793</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.002496878901373278</v>
+        <v>0.004307192198293386</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0006658343736995365</v>
+        <v>0.0008010118043845549</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.00519916142557657</v>
+        <v>0.00578443612151478</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.001812816188870159</v>
+        <v>0.001456512692467782</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.003354297693920372</v>
+        <v>0.009685534591194932</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.00104036620890553</v>
+        <v>0.001056635672020356</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0007906783187681899</v>
+        <v>0.0005450733752620062</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0007490636704119757</v>
+        <v>0.0002844372206420087</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.00524109014675056</v>
+        <v>0.000463743676222661</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.00125786163522017</v>
+        <v>0.002403035413153498</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0001264755480607338</v>
+        <v>0.0003776751993286198</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.001677148846960208</v>
+        <v>0.0002496878901373512</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001257861635220159</v>
+        <v>0.001706200582605111</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.002767295597484309</v>
+        <v>0.005870020964360556</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.001165210153974205</v>
+        <v>0.0003357112882921065</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.00491052850603414</v>
+        <v>0.002621722846441976</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.01513626834381555</v>
+        <v>0.003566932438103276</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0009696458684654519</v>
+        <v>0.001053962900505967</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01106918238993714</v>
+        <v>0.001997503121098665</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001426772975241242</v>
+        <v>0.002161729383506816</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.006540880503144686</v>
+        <v>0.0006745362563238322</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0004215851602023757</v>
+        <v>0.003063365505665183</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.001257861635220148</v>
+        <v>0.0004637436762226499</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.008343815513626862</v>
+        <v>0.001521216973578843</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.001539741989180199</v>
+        <v>0.001414898044111557</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.005073375262054547</v>
+        <v>0.00239739943112558</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.001970649895178222</v>
+        <v>0.001718078875439266</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0002935010482180811</v>
+        <v>0.0006247559547051806</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.001081980857261744</v>
+        <v>0.0003745318352060267</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0009437672040896628</v>
+        <v>0.001091061686949268</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001581356637536413</v>
+        <v>0.00144115292233784</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.001290054099042881</v>
+        <v>0.001180438448566645</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.000632377740303569</v>
+        <v>0.0007588532883642917</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.00285354595048255</v>
+        <v>0.003438155136268317</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.001290054099042859</v>
+        <v>0.003786933000416159</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0005870020964361067</v>
+        <v>0.00113207547169808</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.003102725366876347</v>
+        <v>0.001048218029350057</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0004063388866314854</v>
+        <v>0.0007028504490433352</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.001341719077568171</v>
+        <v>0.001306913996627368</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.007295597484276772</v>
+        <v>0.002475870751154063</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0002098195551825111</v>
+        <v>8.385744234800097e-05</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001081980857261755</v>
+        <v>0.0016399843811011</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.001561248999199327</v>
+        <v>0.001054275673564997</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0004003202562049557</v>
+        <v>0.0005282405526208733</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0006638032018743023</v>
+        <v>0.001091061686949291</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.000976181179226887</v>
+        <v>0.001928721174004155</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.001373283395755298</v>
+        <v>0.001539741989180221</v>
       </c>
       <c r="EL9" t="n">
-        <v>4.06338886631441e-05</v>
+        <v>0.0003329171868498015</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0003145890680298358</v>
+        <v>0.0004161464835622519</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.001138279932546393</v>
+        <v>0.0004876066639577292</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0002101723413198697</v>
+        <v>0.00024968789013734</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0008431703204047402</v>
+        <v>0.001593291404612118</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>0.0002958579881657153</v>
       </c>
       <c r="ES9" t="n">
-        <v>0</v>
+        <v>0.0008010118043845326</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.003480083857442395</v>
+        <v>0.002012578616352179</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.00268569030633653</v>
+        <v>0.001120896717373876</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.001928721174004233</v>
+        <v>0.0001264755480607227</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.001215932914046147</v>
+        <v>2.220446049250313e-17</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0006725514922235831</v>
+        <v>0.004318658280922383</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001498127340823974</v>
+        <v>0.001120896717373876</v>
       </c>
     </row>
   </sheetData>
